--- a/Income_Forecast_ForecastAmount.xlsx
+++ b/Income_Forecast_ForecastAmount.xlsx
@@ -951,10 +951,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>· Forecast and all amounts are GBP.   · Dates are the first of the month (shown as Sep-2026).   · Demo engagements M-1001/1002/1003 are examples — delete them once you add your own.</t>
+          <t>· Forecast and all amounts are GBP.   · The Dashboard's Unallocated Fee (£) column = total fee minus the forecast you've entered: amber = fee still to spread, red = over-forecast, blank = fully forecast.   · Dates are the first of the month (shown as Sep-2026).   · Demo engagements M-1001/1002/1003 are examples — delete them once you add your own.</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4941,6 +4941,7 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5023,6 +5024,11 @@
           <t>Open Var (#)</t>
         </is>
       </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Unallocated Fee (£)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="n">
@@ -5076,6 +5082,10 @@
         <f>IF($F5="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F5,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v>2</v>
       </c>
+      <c r="O5" s="17">
+        <f>IF($F5="","",I5-J5)</f>
+        <v>66000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="22" t="n">
@@ -5129,6 +5139,10 @@
         <f>IF($F6="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F6,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v>0</v>
       </c>
+      <c r="O6" s="17">
+        <f>IF($F6="","",I6-J6)</f>
+        <v>63000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="22" t="n">
@@ -5182,6 +5196,10 @@
         <f>IF($F7="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F7,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v>0</v>
       </c>
+      <c r="O7" s="17">
+        <f>IF($F7="","",I7-J7)</f>
+        <v>21000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="22" t="n">
@@ -5235,6 +5253,10 @@
         <f>IF($F8="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F8,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O8" s="17" t="str">
+        <f>IF($F8="","",I8-J8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="n">
@@ -5288,6 +5310,10 @@
         <f>IF($F9="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F9,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O9" s="17" t="str">
+        <f>IF($F9="","",I9-J9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="n">
@@ -5341,6 +5367,10 @@
         <f>IF($F10="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F10,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O10" s="17" t="str">
+        <f>IF($F10="","",I10-J10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="n">
@@ -5394,6 +5424,10 @@
         <f>IF($F11="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F11,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O11" s="17" t="str">
+        <f>IF($F11="","",I11-J11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="22" t="n">
@@ -5447,6 +5481,10 @@
         <f>IF($F12="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F12,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O12" s="17" t="str">
+        <f>IF($F12="","",I12-J12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="n">
@@ -5500,6 +5538,10 @@
         <f>IF($F13="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F13,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O13" s="17" t="str">
+        <f>IF($F13="","",I13-J13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="22" t="n">
@@ -5553,6 +5595,10 @@
         <f>IF($F14="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F14,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O14" s="17" t="str">
+        <f>IF($F14="","",I14-J14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="n">
@@ -5606,6 +5652,10 @@
         <f>IF($F15="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F15,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O15" s="17" t="str">
+        <f>IF($F15="","",I15-J15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="22" t="n">
@@ -5659,6 +5709,10 @@
         <f>IF($F16="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F16,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O16" s="17" t="str">
+        <f>IF($F16="","",I16-J16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
@@ -5714,6 +5768,10 @@
         <f>IF($F17="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F17,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O17" s="17" t="str">
+        <f>IF($F17="","",I17-J17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="F18" s="23" t="str">
@@ -5752,6 +5810,10 @@
         <f>IF($F18="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F18,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O18" s="17" t="str">
+        <f>IF($F18="","",I18-J18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
@@ -5793,6 +5855,10 @@
       </c>
       <c r="N19" s="26" t="str">
         <f>IF($F19="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F19,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
+      <c r="O19" s="17" t="str">
+        <f>IF($F19="","",I19-J19)</f>
         <v/>
       </c>
     </row>
@@ -5842,6 +5908,10 @@
         <f>IF($F20="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F20,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O20" s="17" t="str">
+        <f>IF($F20="","",I20-J20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
@@ -5889,6 +5959,10 @@
         <f>IF($F21="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F21,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O21" s="17" t="str">
+        <f>IF($F21="","",I21-J21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
@@ -5936,6 +6010,10 @@
         <f>IF($F22="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F22,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O22" s="17" t="str">
+        <f>IF($F22="","",I22-J22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="F23" s="23" t="str">
@@ -5974,6 +6052,10 @@
         <f>IF($F23="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F23,'Forecast Log'!$P$5:$P$64,"YES"))</f>
         <v/>
       </c>
+      <c r="O23" s="17" t="str">
+        <f>IF($F23="","",I23-J23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="F24" s="23" t="str">
@@ -6010,6 +6092,10 @@
       </c>
       <c r="N24" s="26" t="str">
         <f>IF($F24="","",COUNTIFS('Forecast Log'!$A$5:$A$64,$F24,'Forecast Log'!$P$5:$P$64,"YES"))</f>
+        <v/>
+      </c>
+      <c r="O24" s="17" t="str">
+        <f>IF($F24="","",I24-J24)</f>
         <v/>
       </c>
     </row>
@@ -6094,13 +6180,21 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O5:O24">
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I28:I29">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="0">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B20">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Income_Forecast_ForecastAmount.xlsx
+++ b/Income_Forecast_ForecastAmount.xlsx
@@ -951,10 +951,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="90" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>· Forecast and all amounts are GBP.   · The Dashboard's Unallocated Fee (£) column = total fee minus the forecast you've entered: amber = fee still to spread, red = over-forecast, blank = fully forecast.   · Dates are the first of the month (shown as Sep-2026).   · Demo engagements M-1001/1002/1003 are examples — delete them once you add your own.</t>
+          <t>· Forecast and all amounts are GBP.   · The Dashboard's Unallocated Fee (£) = fee not yet covered by actuals or by forecast on months still open. Months that already have an actual are counted at their actual, so the original forecast row stays untouched and re-spreading a variance across future months reconciles back to zero: amber = fee still to spread, red = over-forecast, blank = fully forecast.   · Dates are the first of the month (shown as Sep-2026).   · Demo engagements M-1001/1002/1003 are examples — delete them once you add your own.</t>
         </is>
       </c>
     </row>
@@ -5083,8 +5083,8 @@
         <v>2</v>
       </c>
       <c r="O5" s="17">
-        <f>IF($F5="","",I5-J5)</f>
-        <v>66000</v>
+        <f>IF($F5="","",L5-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F5)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
+        <v>67000</v>
       </c>
     </row>
     <row r="6">
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="17">
-        <f>IF($F6="","",I6-J6)</f>
+        <f>IF($F6="","",L6-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F6)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v>63000</v>
       </c>
     </row>
@@ -5197,8 +5197,8 @@
         <v>0</v>
       </c>
       <c r="O7" s="17">
-        <f>IF($F7="","",I7-J7)</f>
-        <v>21000</v>
+        <f>IF($F7="","",L7-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F7)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
+        <v>22000</v>
       </c>
     </row>
     <row r="8">
@@ -5254,7 +5254,7 @@
         <v/>
       </c>
       <c r="O8" s="17" t="str">
-        <f>IF($F8="","",I8-J8)</f>
+        <f>IF($F8="","",L8-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F8)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
         <v/>
       </c>
       <c r="O9" s="17" t="str">
-        <f>IF($F9="","",I9-J9)</f>
+        <f>IF($F9="","",L9-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F9)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
         <v/>
       </c>
       <c r="O10" s="17" t="str">
-        <f>IF($F10="","",I10-J10)</f>
+        <f>IF($F10="","",L10-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F10)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v/>
       </c>
       <c r="O11" s="17" t="str">
-        <f>IF($F11="","",I11-J11)</f>
+        <f>IF($F11="","",L11-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F11)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
         <v/>
       </c>
       <c r="O12" s="17" t="str">
-        <f>IF($F12="","",I12-J12)</f>
+        <f>IF($F12="","",L12-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F12)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5539,7 +5539,7 @@
         <v/>
       </c>
       <c r="O13" s="17" t="str">
-        <f>IF($F13="","",I13-J13)</f>
+        <f>IF($F13="","",L13-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F13)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
         <v/>
       </c>
       <c r="O14" s="17" t="str">
-        <f>IF($F14="","",I14-J14)</f>
+        <f>IF($F14="","",L14-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F14)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5653,7 +5653,7 @@
         <v/>
       </c>
       <c r="O15" s="17" t="str">
-        <f>IF($F15="","",I15-J15)</f>
+        <f>IF($F15="","",L15-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F15)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5710,7 +5710,7 @@
         <v/>
       </c>
       <c r="O16" s="17" t="str">
-        <f>IF($F16="","",I16-J16)</f>
+        <f>IF($F16="","",L16-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F16)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
         <v/>
       </c>
       <c r="O17" s="17" t="str">
-        <f>IF($F17="","",I17-J17)</f>
+        <f>IF($F17="","",L17-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F17)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
         <v/>
       </c>
       <c r="O18" s="17" t="str">
-        <f>IF($F18="","",I18-J18)</f>
+        <f>IF($F18="","",L18-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F18)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5858,7 +5858,7 @@
         <v/>
       </c>
       <c r="O19" s="17" t="str">
-        <f>IF($F19="","",I19-J19)</f>
+        <f>IF($F19="","",L19-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F19)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
         <v/>
       </c>
       <c r="O20" s="17" t="str">
-        <f>IF($F20="","",I20-J20)</f>
+        <f>IF($F20="","",L20-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F20)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
         <v/>
       </c>
       <c r="O21" s="17" t="str">
-        <f>IF($F21="","",I21-J21)</f>
+        <f>IF($F21="","",L21-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F21)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
         <v/>
       </c>
       <c r="O22" s="17" t="str">
-        <f>IF($F22="","",I22-J22)</f>
+        <f>IF($F22="","",L22-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F22)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
         <v/>
       </c>
       <c r="O23" s="17" t="str">
-        <f>IF($F23="","",I23-J23)</f>
+        <f>IF($F23="","",L23-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F23)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
         <v/>
       </c>
       <c r="O24" s="17" t="str">
-        <f>IF($F24="","",I24-J24)</f>
+        <f>IF($F24="","",L24-SUMPRODUCT(('Forecast Log'!$A$5:$A$64=$F24)*('Forecast Log'!$G$5:$G$64="")*'Forecast Log'!$D$5:$D$64))</f>
         <v/>
       </c>
     </row>
